--- a/Figure 4/Figure 4-A.xlsx
+++ b/Figure 4/Figure 4-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F36671-5581-4A2D-962F-1676D467AD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8B203A-FBFE-4A51-8880-2208ADA05FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31880" yWindow="2160" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
@@ -93,8 +93,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -414,7 +414,8 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="10.81640625"/>
+    <col min="1" max="9" width="10.81640625" style="1"/>
+    <col min="10" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -636,10 +637,6 @@
       <c r="E8" s="1">
         <v>3566.0498015910321</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
